--- a/ConfigWorkspace/Data/player.xlsx
+++ b/ConfigWorkspace/Data/player.xlsx
@@ -653,11 +653,11 @@
           <t>玩家</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>100</v>
-      </c>
-      <c r="E5" t="n">
-        <v>10</v>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>0.8</v>

--- a/ConfigWorkspace/Data/player.xlsx
+++ b/ConfigWorkspace/Data/player.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -422,54 +422,79 @@
           <t>##var</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>max_hp</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>contact_damage</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>invulnerable_duration</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>retry_delay</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>attack_interval</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>knockback_impulse</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>knockback_speed_limit</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>contact_radius</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>water_capacity</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>water_start</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>earth_capacity</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>earth_start</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>life_heal_interval</t>
         </is>
       </c>
     </row>
@@ -479,54 +504,79 @@
           <t>##type</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>string!</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>float!#range=[1,99999]</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>float!#range=[0,9999]</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>float!#range=[0,10]</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>float!#range=[0,60]</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>float!#range=[0.01,10]</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>float!#range=[0,100]</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>float!#range=[0,100]</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>float!#range=[0.05,10]</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>int!#range=[0,99]</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>int!#range=[0,99]</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>int!#range=[0,99]</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>int!#range=[0,99]</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>float!#range=[0.1,60]</t>
         </is>
       </c>
     </row>
@@ -536,21 +586,6 @@
           <t>##group</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>c</t>
@@ -582,6 +617,46 @@
         </is>
       </c>
       <c r="K3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>c</t>
         </is>
@@ -593,89 +668,129 @@
           <t>##comment</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>编号</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>显示名</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>血量上限</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>敌人贴身一次造成的伤害</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>受击无敌时长</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>打空后重来延时</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>攻击间隔</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>受击被推开的冲量</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>受击期间的速度上限</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>敌人贴身判定的圆心距（世界单位）</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>水弹药上限</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>开局水弹药</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>土弹药上限</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>开局土弹药</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>神泉回血所需静止秒数</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" t="n">
+      <c r="E5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>玩家</t>
         </is>
       </c>
-      <c r="D5">
+      <c r="G5" t="n">
         <v>3</v>
       </c>
-      <c r="E5">
+      <c r="H5" t="n">
         <v>1</v>
       </c>
-      <c r="F5" t="n">
+      <c r="I5" t="n">
         <v>0.8</v>
       </c>
-      <c r="G5" t="n">
+      <c r="J5" t="n">
         <v>1.2</v>
       </c>
-      <c r="H5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L5" t="n">
         <v>12</v>
       </c>
-      <c r="J5" t="n">
+      <c r="M5" t="n">
         <v>12</v>
       </c>
-      <c r="K5" t="n">
+      <c r="N5" t="n">
         <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>5</v>
+      </c>
+      <c r="P5" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>5</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/ConfigWorkspace/Data/player.xlsx
+++ b/ConfigWorkspace/Data/player.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98D62E7C-4D31-4560-B5F9-69C5A4C760DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01E302AF-1A8B-45B6-A527-BC7B797A161F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3945" yWindow="3810" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="255" yWindow="3060" windowWidth="12660" windowHeight="15300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="45">
   <si>
     <t>##var</t>
   </si>
@@ -33,139 +33,138 @@
     <t>id</t>
   </si>
   <si>
+    <t>max_hp</t>
+  </si>
+  <si>
+    <t>invulnerable_duration</t>
+  </si>
+  <si>
+    <t>retry_delay</t>
+  </si>
+  <si>
+    <t>attack_interval</t>
+  </si>
+  <si>
+    <t>knockback_impulse</t>
+  </si>
+  <si>
+    <t>knockback_speed_limit</t>
+  </si>
+  <si>
+    <t>contact_radius</t>
+  </si>
+  <si>
+    <t>water_capacity</t>
+  </si>
+  <si>
+    <t>water_start</t>
+  </si>
+  <si>
+    <t>earth_capacity</t>
+  </si>
+  <si>
+    <t>earth_start</t>
+  </si>
+  <si>
+    <t>life_heal_interval</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>float!#range=[1,99999]</t>
+  </si>
+  <si>
+    <t>float!#range=[0,10]</t>
+  </si>
+  <si>
+    <t>float!#range=[0,60]</t>
+  </si>
+  <si>
+    <t>float!#range=[0.01,10]</t>
+  </si>
+  <si>
+    <t>float!#range=[0,100]</t>
+  </si>
+  <si>
+    <t>float!#range=[0.05,10]</t>
+  </si>
+  <si>
+    <t>int!#range=[0,99]</t>
+  </si>
+  <si>
+    <t>float!#range=[0.1,60]</t>
+  </si>
+  <si>
+    <t>##group</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>##comment</t>
+  </si>
+  <si>
+    <t>编号</t>
+  </si>
+  <si>
+    <t>血量上限</t>
+  </si>
+  <si>
+    <t>受击无敌时长</t>
+  </si>
+  <si>
+    <t>打空后重来延时</t>
+  </si>
+  <si>
+    <t>攻击间隔</t>
+  </si>
+  <si>
+    <t>受击被推开的冲量</t>
+  </si>
+  <si>
+    <t>受击期间的速度上限</t>
+  </si>
+  <si>
+    <t>敌人贴身判定的圆心距（世界单位）</t>
+  </si>
+  <si>
+    <t>水弹药上限</t>
+  </si>
+  <si>
+    <t>开局水弹药</t>
+  </si>
+  <si>
+    <t>土弹药上限</t>
+  </si>
+  <si>
+    <t>开局土弹药</t>
+  </si>
+  <si>
+    <t>神泉回血所需静止秒数</t>
+  </si>
+  <si>
     <t>name</t>
-  </si>
-  <si>
-    <t>max_hp</t>
-  </si>
-  <si>
-    <t>contact_damage</t>
-  </si>
-  <si>
-    <t>invulnerable_duration</t>
-  </si>
-  <si>
-    <t>retry_delay</t>
-  </si>
-  <si>
-    <t>attack_interval</t>
-  </si>
-  <si>
-    <t>knockback_impulse</t>
-  </si>
-  <si>
-    <t>knockback_speed_limit</t>
-  </si>
-  <si>
-    <t>contact_radius</t>
-  </si>
-  <si>
-    <t>water_capacity</t>
-  </si>
-  <si>
-    <t>water_start</t>
-  </si>
-  <si>
-    <t>earth_capacity</t>
-  </si>
-  <si>
-    <t>earth_start</t>
-  </si>
-  <si>
-    <t>life_heal_interval</t>
-  </si>
-  <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>string!</t>
-  </si>
-  <si>
-    <t>float!#range=[1,99999]</t>
-  </si>
-  <si>
-    <t>float!#range=[0,9999]</t>
-  </si>
-  <si>
-    <t>float!#range=[0,10]</t>
-  </si>
-  <si>
-    <t>float!#range=[0,60]</t>
-  </si>
-  <si>
-    <t>float!#range=[0.01,10]</t>
-  </si>
-  <si>
-    <t>float!#range=[0,100]</t>
-  </si>
-  <si>
-    <t>float!#range=[0.05,10]</t>
-  </si>
-  <si>
-    <t>int!#range=[0,99]</t>
-  </si>
-  <si>
-    <t>float!#range=[0.1,60]</t>
-  </si>
-  <si>
-    <t>##group</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>c</t>
-  </si>
-  <si>
-    <t>##comment</t>
-  </si>
-  <si>
-    <t>编号</t>
-  </si>
-  <si>
-    <t>显示名</t>
-  </si>
-  <si>
-    <t>血量上限</t>
-  </si>
-  <si>
-    <t>敌人贴身一次造成的伤害</t>
-  </si>
-  <si>
-    <t>受击无敌时长</t>
-  </si>
-  <si>
-    <t>打空后重来延时</t>
-  </si>
-  <si>
-    <t>攻击间隔</t>
-  </si>
-  <si>
-    <t>受击被推开的冲量</t>
-  </si>
-  <si>
-    <t>受击期间的速度上限</t>
-  </si>
-  <si>
-    <t>敌人贴身判定的圆心距（世界单位）</t>
-  </si>
-  <si>
-    <t>水弹药上限</t>
-  </si>
-  <si>
-    <t>开局水弹药</t>
-  </si>
-  <si>
-    <t>土弹药上限</t>
-  </si>
-  <si>
-    <t>开局土弹药</t>
-  </si>
-  <si>
-    <t>神泉回血所需静止秒数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玩家名字</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>玩家</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -512,26 +511,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="2" width="5.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.25" customWidth="1"/>
-    <col min="5" max="5" width="21.375" customWidth="1"/>
-    <col min="6" max="6" width="11.75" customWidth="1"/>
-    <col min="7" max="7" width="14.5" customWidth="1"/>
-    <col min="8" max="8" width="9.5" customWidth="1"/>
-    <col min="9" max="9" width="16.875" customWidth="1"/>
-    <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="20.375" customWidth="1"/>
-    <col min="12" max="13" width="10.625" customWidth="1"/>
-    <col min="14" max="14" width="11.25" customWidth="1"/>
-    <col min="15" max="15" width="12.375" customWidth="1"/>
-    <col min="16" max="16" width="19.875" customWidth="1"/>
+    <col min="5" max="5" width="11.75" customWidth="1"/>
+    <col min="6" max="6" width="14.5" customWidth="1"/>
+    <col min="7" max="7" width="9.5" customWidth="1"/>
+    <col min="8" max="8" width="16.875" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
+    <col min="10" max="10" width="20.375" customWidth="1"/>
+    <col min="11" max="12" width="10.625" customWidth="1"/>
+    <col min="13" max="13" width="11.25" customWidth="1"/>
+    <col min="14" max="14" width="12.375" customWidth="1"/>
+    <col min="15" max="15" width="19.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -539,228 +537,216 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="B2" t="s">
         <v>15</v>
       </c>
+      <c r="C2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" t="s">
+        <v>22</v>
+      </c>
+      <c r="O2" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" t="s">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A3" t="s">
         <v>24</v>
       </c>
-      <c r="J2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M3" t="s">
+        <v>25</v>
+      </c>
+      <c r="N3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A4" t="s">
         <v>26</v>
       </c>
-      <c r="M2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O2" t="s">
-        <v>26</v>
-      </c>
-      <c r="P2" t="s">
+      <c r="B4" t="s">
         <v>27</v>
       </c>
+      <c r="C4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" t="s">
+        <v>35</v>
+      </c>
+      <c r="L4" t="s">
+        <v>36</v>
+      </c>
+      <c r="M4" t="s">
+        <v>37</v>
+      </c>
+      <c r="N4" t="s">
+        <v>38</v>
+      </c>
+      <c r="O4" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I3" t="s">
-        <v>29</v>
-      </c>
-      <c r="J3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L3" t="s">
-        <v>29</v>
-      </c>
-      <c r="M3" t="s">
-        <v>29</v>
-      </c>
-      <c r="N3" t="s">
-        <v>29</v>
-      </c>
-      <c r="O3" t="s">
-        <v>29</v>
-      </c>
-      <c r="P3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G4" t="s">
-        <v>36</v>
-      </c>
-      <c r="H4" t="s">
-        <v>37</v>
-      </c>
-      <c r="I4" t="s">
-        <v>38</v>
-      </c>
-      <c r="J4" t="s">
-        <v>39</v>
-      </c>
-      <c r="K4" t="s">
-        <v>40</v>
-      </c>
-      <c r="L4" t="s">
-        <v>41</v>
-      </c>
-      <c r="M4" t="s">
-        <v>42</v>
-      </c>
-      <c r="N4" t="s">
-        <v>43</v>
-      </c>
-      <c r="O4" t="s">
-        <v>44</v>
-      </c>
-      <c r="P4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.15">
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D5">
         <v>3</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F5">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="G5">
-        <v>1.2</v>
+        <v>0.35</v>
       </c>
       <c r="H5">
-        <v>0.35</v>
+        <v>12</v>
       </c>
       <c r="I5">
         <v>12</v>
       </c>
       <c r="J5">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L5">
         <v>5</v>
@@ -772,9 +758,6 @@
         <v>5</v>
       </c>
       <c r="O5">
-        <v>5</v>
-      </c>
-      <c r="P5">
         <v>3</v>
       </c>
     </row>

--- a/ConfigWorkspace/Data/player.xlsx
+++ b/ConfigWorkspace/Data/player.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01E302AF-1A8B-45B6-A527-BC7B797A161F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E23E38-6868-49C2-96DB-56A89C804A25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="255" yWindow="3060" windowWidth="12660" windowHeight="15300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="255" yWindow="3060" windowWidth="23445" windowHeight="15300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -725,7 +725,7 @@
         <v>44</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>999</v>
       </c>
       <c r="E5">
         <v>0.8</v>

--- a/ConfigWorkspace/Data/player.xlsx
+++ b/ConfigWorkspace/Data/player.xlsx
@@ -1,31 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E23E38-6868-49C2-96DB-56A89C804A25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="255" yWindow="3060" windowWidth="23445" windowHeight="15300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="14940" windowHeight="9900"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="44">
   <si>
     <t>##var</t>
   </si>
@@ -33,6 +35,9 @@
     <t>id</t>
   </si>
   <si>
+    <t>name</t>
+  </si>
+  <si>
     <t>max_hp</t>
   </si>
   <si>
@@ -75,6 +80,9 @@
     <t>int</t>
   </si>
   <si>
+    <t>string!</t>
+  </si>
+  <si>
     <t>float!#range=[1,99999]</t>
   </si>
   <si>
@@ -111,6 +119,9 @@
     <t>编号</t>
   </si>
   <si>
+    <t>玩家名字</t>
+  </si>
+  <si>
     <t>血量上限</t>
   </si>
   <si>
@@ -147,55 +158,374 @@
     <t>神泉回血所需静止秒数</t>
   </si>
   <si>
-    <t>name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>string!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>c</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>玩家名字</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>玩家</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -203,24 +533,310 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -505,31 +1121,31 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:O5"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4"/>
   <cols>
-    <col min="2" max="2" width="5.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.25" customWidth="1"/>
-    <col min="5" max="5" width="11.75" customWidth="1"/>
+    <col min="2" max="2" width="5.25454545454545" customWidth="1"/>
+    <col min="3" max="3" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.2545454545455" customWidth="1"/>
+    <col min="5" max="5" width="11.7545454545455" customWidth="1"/>
     <col min="6" max="6" width="14.5" customWidth="1"/>
     <col min="7" max="7" width="9.5" customWidth="1"/>
-    <col min="8" max="8" width="16.875" customWidth="1"/>
+    <col min="8" max="8" width="16.8727272727273" customWidth="1"/>
     <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="20.375" customWidth="1"/>
-    <col min="11" max="12" width="10.625" customWidth="1"/>
-    <col min="13" max="13" width="11.25" customWidth="1"/>
-    <col min="14" max="14" width="12.375" customWidth="1"/>
-    <col min="15" max="15" width="19.875" customWidth="1"/>
+    <col min="10" max="10" width="20.3727272727273" customWidth="1"/>
+    <col min="11" max="12" width="10.6272727272727" customWidth="1"/>
+    <col min="13" max="13" width="11.2545454545455" customWidth="1"/>
+    <col min="14" max="14" width="12.3727272727273" customWidth="1"/>
+    <col min="15" max="15" width="19.8727272727273" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -537,195 +1153,195 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4" t="s">
+        <v>37</v>
+      </c>
+      <c r="K4" t="s">
+        <v>38</v>
+      </c>
+      <c r="L4" t="s">
+        <v>39</v>
+      </c>
+      <c r="M4" t="s">
         <v>40</v>
       </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" t="s">
-        <v>13</v>
+      <c r="N4" t="s">
+        <v>41</v>
+      </c>
+      <c r="O4" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M2" t="s">
-        <v>22</v>
-      </c>
-      <c r="N2" t="s">
-        <v>22</v>
-      </c>
-      <c r="O2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M3" t="s">
-        <v>25</v>
-      </c>
-      <c r="N3" t="s">
-        <v>25</v>
-      </c>
-      <c r="O3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J4" t="s">
-        <v>34</v>
-      </c>
-      <c r="K4" t="s">
-        <v>35</v>
-      </c>
-      <c r="L4" t="s">
-        <v>36</v>
-      </c>
-      <c r="M4" t="s">
-        <v>37</v>
-      </c>
-      <c r="N4" t="s">
-        <v>38</v>
-      </c>
-      <c r="O4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:15">
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D5">
-        <v>999</v>
+        <v>5</v>
       </c>
       <c r="E5">
         <v>0.8</v>
@@ -762,8 +1378,8 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/ConfigWorkspace/Data/player.xlsx
+++ b/ConfigWorkspace/Data/player.xlsx
@@ -1,31 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E23E38-6868-49C2-96DB-56A89C804A25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="255" yWindow="3060" windowWidth="23445" windowHeight="15300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="44">
   <si>
     <t>##var</t>
   </si>
@@ -33,6 +35,9 @@
     <t>id</t>
   </si>
   <si>
+    <t>name</t>
+  </si>
+  <si>
     <t>max_hp</t>
   </si>
   <si>
@@ -75,6 +80,9 @@
     <t>int</t>
   </si>
   <si>
+    <t>string!</t>
+  </si>
+  <si>
     <t>float!#range=[1,99999]</t>
   </si>
   <si>
@@ -111,6 +119,9 @@
     <t>编号</t>
   </si>
   <si>
+    <t>玩家名字</t>
+  </si>
+  <si>
     <t>血量上限</t>
   </si>
   <si>
@@ -147,55 +158,374 @@
     <t>神泉回血所需静止秒数</t>
   </si>
   <si>
-    <t>name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>string!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>c</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>玩家名字</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>玩家</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -203,24 +533,310 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -505,31 +1121,31 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:O5"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4"/>
   <cols>
-    <col min="2" max="2" width="5.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.25" customWidth="1"/>
-    <col min="5" max="5" width="11.75" customWidth="1"/>
+    <col min="2" max="2" width="5.25454545454545" customWidth="1"/>
+    <col min="3" max="3" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.2545454545455" customWidth="1"/>
+    <col min="5" max="5" width="11.7545454545455" customWidth="1"/>
     <col min="6" max="6" width="14.5" customWidth="1"/>
     <col min="7" max="7" width="9.5" customWidth="1"/>
-    <col min="8" max="8" width="16.875" customWidth="1"/>
+    <col min="8" max="8" width="16.8727272727273" customWidth="1"/>
     <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="20.375" customWidth="1"/>
-    <col min="11" max="12" width="10.625" customWidth="1"/>
-    <col min="13" max="13" width="11.25" customWidth="1"/>
-    <col min="14" max="14" width="12.375" customWidth="1"/>
-    <col min="15" max="15" width="19.875" customWidth="1"/>
+    <col min="10" max="10" width="20.3727272727273" customWidth="1"/>
+    <col min="11" max="12" width="10.6272727272727" customWidth="1"/>
+    <col min="13" max="13" width="11.2545454545455" customWidth="1"/>
+    <col min="14" max="14" width="12.3727272727273" customWidth="1"/>
+    <col min="15" max="15" width="19.8727272727273" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -537,195 +1153,195 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4" t="s">
+        <v>37</v>
+      </c>
+      <c r="K4" t="s">
+        <v>38</v>
+      </c>
+      <c r="L4" t="s">
+        <v>39</v>
+      </c>
+      <c r="M4" t="s">
         <v>40</v>
       </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" t="s">
-        <v>13</v>
+      <c r="N4" t="s">
+        <v>41</v>
+      </c>
+      <c r="O4" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M2" t="s">
-        <v>22</v>
-      </c>
-      <c r="N2" t="s">
-        <v>22</v>
-      </c>
-      <c r="O2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M3" t="s">
-        <v>25</v>
-      </c>
-      <c r="N3" t="s">
-        <v>25</v>
-      </c>
-      <c r="O3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J4" t="s">
-        <v>34</v>
-      </c>
-      <c r="K4" t="s">
-        <v>35</v>
-      </c>
-      <c r="L4" t="s">
-        <v>36</v>
-      </c>
-      <c r="M4" t="s">
-        <v>37</v>
-      </c>
-      <c r="N4" t="s">
-        <v>38</v>
-      </c>
-      <c r="O4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:15">
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D5">
-        <v>999</v>
+        <v>3</v>
       </c>
       <c r="E5">
         <v>0.8</v>
@@ -762,8 +1378,8 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/ConfigWorkspace/Data/player.xlsx
+++ b/ConfigWorkspace/Data/player.xlsx
@@ -8,26 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8AFF811-C261-4D56-83DA-15E7B62321BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{697BC1DE-5F0B-44C0-A60A-DAF6857C843E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3750" yWindow="6135" windowWidth="24405" windowHeight="13635" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4095" yWindow="5055" windowWidth="26760" windowHeight="13965" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -36,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="48">
   <si>
     <t>##var</t>
   </si>
@@ -168,13 +157,42 @@
   </si>
   <si>
     <t>玩家</t>
+  </si>
+  <si>
+    <t>seed_capacity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>i</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>nt!#range=[1,99]</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>c</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>种子使用次数上限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -185,6 +203,14 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -209,9 +235,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -516,7 +545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -533,10 +562,11 @@
     <col min="13" max="13" width="11.25" style="1" customWidth="1"/>
     <col min="14" max="14" width="12.375" style="1" customWidth="1"/>
     <col min="15" max="15" width="19.875" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="1"/>
+    <col min="16" max="16" width="19.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -582,8 +612,11 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="P1" s="1" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>15</v>
       </c>
@@ -629,8 +662,11 @@
       <c r="O2" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="P2" s="2" t="s">
+        <v>45</v>
+      </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>26</v>
       </c>
@@ -676,8 +712,11 @@
       <c r="O3" s="1" t="s">
         <v>27</v>
       </c>
+      <c r="P3" s="2" t="s">
+        <v>46</v>
+      </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>28</v>
       </c>
@@ -723,8 +762,11 @@
       <c r="O4" s="1" t="s">
         <v>42</v>
       </c>
+      <c r="P4" s="2" t="s">
+        <v>47</v>
+      </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.15">
       <c r="B5" s="1">
         <v>1</v>
       </c>
@@ -765,12 +807,15 @@
         <v>5</v>
       </c>
       <c r="O5" s="1">
+        <v>3</v>
+      </c>
+      <c r="P5" s="1">
         <v>3</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/ConfigWorkspace/Data/player.xlsx
+++ b/ConfigWorkspace/Data/player.xlsx
@@ -1,31 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{697BC1DE-5F0B-44C0-A60A-DAF6857C843E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4095" yWindow="5055" windowWidth="26760" windowHeight="13965" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="23120" windowHeight="13660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="47">
   <si>
     <t>##var</t>
   </si>
@@ -72,6 +74,9 @@
     <t>life_heal_interval</t>
   </si>
   <si>
+    <t>seed_capacity</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -105,65 +110,14 @@
     <t>float!#range=[0.1,60]</t>
   </si>
   <si>
-    <t>##group</t>
-  </si>
-  <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t>##comment</t>
-  </si>
-  <si>
-    <t>编号</t>
-  </si>
-  <si>
-    <t>玩家名字</t>
-  </si>
-  <si>
-    <t>血量上限</t>
-  </si>
-  <si>
-    <t>受击无敌时长</t>
-  </si>
-  <si>
-    <t>打空后重来延时</t>
-  </si>
-  <si>
-    <t>攻击间隔</t>
-  </si>
-  <si>
-    <t>受击被推开的冲量</t>
-  </si>
-  <si>
-    <t>受击期间的速度上限</t>
-  </si>
-  <si>
-    <t>敌人贴身判定的圆心距（世界单位）</t>
-  </si>
-  <si>
-    <t>水弹药上限</t>
-  </si>
-  <si>
-    <t>开局水弹药</t>
-  </si>
-  <si>
-    <t>土弹药上限</t>
-  </si>
-  <si>
-    <t>开局土弹药</t>
-  </si>
-  <si>
-    <t>神泉回血所需静止秒数</t>
-  </si>
-  <si>
-    <t>玩家</t>
-  </si>
-  <si>
-    <t>seed_capacity</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>i</t>
     </r>
     <r>
@@ -171,28 +125,81 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>nt!#range=[1,99]</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>##group</t>
   </si>
   <si>
     <t>c</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>##comment</t>
+  </si>
+  <si>
+    <t>编号</t>
+  </si>
+  <si>
+    <t>玩家名字</t>
+  </si>
+  <si>
+    <t>血量上限</t>
+  </si>
+  <si>
+    <t>受击无敌时长</t>
+  </si>
+  <si>
+    <t>打空后重来延时</t>
+  </si>
+  <si>
+    <t>攻击间隔</t>
+  </si>
+  <si>
+    <t>受击被推开的冲量</t>
+  </si>
+  <si>
+    <t>受击期间的速度上限</t>
+  </si>
+  <si>
+    <t>敌人贴身判定的圆心距（世界单位）</t>
+  </si>
+  <si>
+    <t>水弹药上限</t>
+  </si>
+  <si>
+    <t>开局水弹药</t>
+  </si>
+  <si>
+    <t>土弹药上限</t>
+  </si>
+  <si>
+    <t>开局土弹药</t>
+  </si>
+  <si>
+    <t>神泉回血所需静止秒数</t>
   </si>
   <si>
     <t>种子使用次数上限</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玩家</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -201,29 +208,345 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -231,30 +554,316 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -539,14 +1148,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:P5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="4"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="5.25" style="1" customWidth="1"/>
@@ -562,11 +1171,11 @@
     <col min="13" max="13" width="11.25" style="1" customWidth="1"/>
     <col min="14" max="14" width="12.375" style="1" customWidth="1"/>
     <col min="15" max="15" width="19.875" style="1" customWidth="1"/>
-    <col min="16" max="16" width="19.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.375" style="1" customWidth="1"/>
     <col min="17" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -613,165 +1222,165 @@
         <v>14</v>
       </c>
       <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" ht="17" spans="1:16">
+      <c r="A2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="O4" s="1" t="s">
         <v>44</v>
       </c>
+      <c r="P4" s="2" t="s">
+        <v>45</v>
+      </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:16">
       <c r="B5" s="1">
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D5" s="1">
         <v>5</v>
@@ -814,8 +1423,8 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>